--- a/Riyadh_Zone_Eng_Log.xlsx
+++ b/Riyadh_Zone_Eng_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\SOCOTEC_VISITS App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1D8785-6A68-429F-89FC-94DF85DFE7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DB2763-D174-4549-A02B-95CE3703C68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1142,22 +1142,6 @@
       </fill>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
@@ -1181,13 +1165,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="5">
     <tableStyle name="Sheet1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="secondRowStripe" dxfId="9"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="secondRowStripe" dxfId="8"/>
     </tableStyle>
     <tableStyle name="Sheet1-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -3971,11 +3971,11 @@
       </c>
     </row>
     <row r="109" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A109" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B109" s="10" t="s">
-        <v>149</v>
+      <c r="A109" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B109" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>150</v>
@@ -3994,11 +3994,11 @@
       </c>
     </row>
     <row r="110" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A110" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B110" s="10" t="s">
-        <v>149</v>
+      <c r="A110" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="C110" s="10" t="s">
         <v>150</v>
@@ -4017,11 +4017,11 @@
       </c>
     </row>
     <row r="111" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A111" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B111" s="10" t="s">
-        <v>149</v>
+      <c r="A111" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B111" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>150</v>
@@ -4040,11 +4040,11 @@
       </c>
     </row>
     <row r="112" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A112" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B112" s="10" t="s">
-        <v>149</v>
+      <c r="A112" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="C112" s="10" t="s">
         <v>150</v>
@@ -4063,11 +4063,11 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A113" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B113" s="10" t="s">
-        <v>149</v>
+      <c r="A113" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B113" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>150</v>
@@ -4086,11 +4086,11 @@
       </c>
     </row>
     <row r="114" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A114" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B114" s="10" t="s">
-        <v>149</v>
+      <c r="A114" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>150</v>
@@ -4109,11 +4109,11 @@
       </c>
     </row>
     <row r="115" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A115" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B115" s="10" t="s">
-        <v>149</v>
+      <c r="A115" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B115" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>150</v>
@@ -4132,11 +4132,11 @@
       </c>
     </row>
     <row r="116" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A116" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B116" s="10" t="s">
-        <v>149</v>
+      <c r="A116" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>150</v>
@@ -4155,11 +4155,11 @@
       </c>
     </row>
     <row r="117" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A117" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B117" s="10" t="s">
-        <v>149</v>
+      <c r="A117" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B117" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="C117" s="10" t="s">
         <v>150</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="118" spans="1:7" ht="22.5" customHeight="1">
       <c r="A118" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B118" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B118" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C118" s="10" t="s">
         <v>150</v>
@@ -4202,10 +4202,10 @@
     </row>
     <row r="119" spans="1:7" ht="22.5" customHeight="1">
       <c r="A119" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B119" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B119" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>150</v>
@@ -4225,10 +4225,10 @@
     </row>
     <row r="120" spans="1:7" ht="22.5" customHeight="1">
       <c r="A120" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B120" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B120" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>150</v>
@@ -4248,10 +4248,10 @@
     </row>
     <row r="121" spans="1:7" ht="22.5" customHeight="1">
       <c r="A121" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B121" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B121" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>150</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="122" spans="1:7" ht="22.5" customHeight="1">
       <c r="A122" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B122" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B122" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>150</v>
@@ -4294,10 +4294,10 @@
     </row>
     <row r="123" spans="1:7" ht="22.5" customHeight="1">
       <c r="A123" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B123" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B123" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>150</v>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="124" spans="1:7" ht="22.5" customHeight="1">
       <c r="A124" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B124" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B124" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>150</v>
@@ -4340,10 +4340,10 @@
     </row>
     <row r="125" spans="1:7" ht="22.5" customHeight="1">
       <c r="A125" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B125" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B125" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>150</v>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="126" spans="1:7" ht="22.5" customHeight="1">
       <c r="A126" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B126" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B126" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>150</v>
@@ -4386,10 +4386,10 @@
     </row>
     <row r="127" spans="1:7" ht="22.5" customHeight="1">
       <c r="A127" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B127" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B127" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>150</v>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="128" spans="1:7" ht="22.5" customHeight="1">
       <c r="A128" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B128" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B128" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>150</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="129" spans="1:7" ht="22.5" customHeight="1">
       <c r="A129" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B129" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B129" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>150</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="130" spans="1:7" ht="22.5" customHeight="1">
       <c r="A130" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B130" s="10" t="s">
-        <v>149</v>
+        <v>107</v>
+      </c>
+      <c r="B130" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>150</v>
@@ -5723,42 +5723,42 @@
     <hyperlink ref="A106" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
     <hyperlink ref="A107" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
     <hyperlink ref="A108" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="A109" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="A110" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="A111" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="A112" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="A113" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="A114" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="A115" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="A116" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="A117" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="A118" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="A119" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="A120" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="A121" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="A122" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="A123" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="A124" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="A125" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="A126" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="A127" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="A128" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="A129" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="A130" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="A156" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="A157" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="A158" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="A159" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="A160" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="A161" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="A162" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="A163" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="A164" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="A165" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="A181" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="A184" r:id="rId109" xr:uid="{F3225E6D-3468-4318-8B91-260F9EF96990}"/>
-    <hyperlink ref="A166" r:id="rId110" xr:uid="{28C032BE-745B-4719-BC4F-5BC8CF6CE6AD}"/>
-    <hyperlink ref="A167:A180" r:id="rId111" display="ayman.ashraf@socotec.com" xr:uid="{74B3E606-0774-48D2-9E42-2C52AF79F7BD}"/>
+    <hyperlink ref="A156" r:id="rId76" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="A157" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="A158" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="A159" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="A160" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="A161" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="A162" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="A163" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="A164" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="A165" r:id="rId85" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="A181" r:id="rId86" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="A184" r:id="rId87" xr:uid="{F3225E6D-3468-4318-8B91-260F9EF96990}"/>
+    <hyperlink ref="A166" r:id="rId88" xr:uid="{28C032BE-745B-4719-BC4F-5BC8CF6CE6AD}"/>
+    <hyperlink ref="A167:A180" r:id="rId89" display="ayman.ashraf@socotec.com" xr:uid="{74B3E606-0774-48D2-9E42-2C52AF79F7BD}"/>
+    <hyperlink ref="A109" r:id="rId90" xr:uid="{B85E91F0-F4EA-411E-88CC-88F74EEC2B12}"/>
+    <hyperlink ref="A110" r:id="rId91" xr:uid="{31B92A57-38BB-4EB0-9730-087D7EE8F96E}"/>
+    <hyperlink ref="A111" r:id="rId92" xr:uid="{AF65F850-7986-4660-98A9-CED467115EE6}"/>
+    <hyperlink ref="A112" r:id="rId93" xr:uid="{FAA039C4-A032-49DC-9FCF-95ECD6932EB3}"/>
+    <hyperlink ref="A113" r:id="rId94" xr:uid="{9E2C83CD-3637-4CE4-916D-D485033DB5E1}"/>
+    <hyperlink ref="A114" r:id="rId95" xr:uid="{41BEEFAF-AD8A-4B84-B398-82653F7106E0}"/>
+    <hyperlink ref="A115" r:id="rId96" xr:uid="{7469C548-438F-45DA-B067-D2855D4DD123}"/>
+    <hyperlink ref="A116" r:id="rId97" xr:uid="{222237D1-C95A-41A2-A813-10E3D5079802}"/>
+    <hyperlink ref="A117" r:id="rId98" xr:uid="{039B2F75-D7CC-4948-A090-EF878C0B6E96}"/>
+    <hyperlink ref="A118" r:id="rId99" xr:uid="{1D2F319C-7082-44EB-ABA8-0F6C7FC5B9DE}"/>
+    <hyperlink ref="A119" r:id="rId100" xr:uid="{22AE1928-7CBF-4A84-8D9F-AEF119A564CA}"/>
+    <hyperlink ref="A120" r:id="rId101" xr:uid="{B1500585-3756-49B3-B698-2222CCE9F14E}"/>
+    <hyperlink ref="A121" r:id="rId102" xr:uid="{968959D0-FA97-450C-ACD2-5CF200080073}"/>
+    <hyperlink ref="A122" r:id="rId103" xr:uid="{569040FD-28EE-485E-AF7B-C1F4A17863D5}"/>
+    <hyperlink ref="A123" r:id="rId104" xr:uid="{F1712F73-9AFA-4A1A-8459-949196FF4947}"/>
+    <hyperlink ref="A124" r:id="rId105" xr:uid="{F3B030FA-01EC-4BBA-8F9D-2F23126EACBA}"/>
+    <hyperlink ref="A125" r:id="rId106" xr:uid="{09036006-CF36-48E2-B1F1-5561E5001113}"/>
+    <hyperlink ref="A126" r:id="rId107" xr:uid="{151F7DF0-58AC-46D8-AF5F-4800D407AF9A}"/>
+    <hyperlink ref="A127" r:id="rId108" xr:uid="{3B52CF30-7D13-48A7-94F4-70F57714E363}"/>
+    <hyperlink ref="A128" r:id="rId109" xr:uid="{089C5B9B-4DAC-4B8F-8F15-F80D0FEC277F}"/>
+    <hyperlink ref="A129" r:id="rId110" xr:uid="{214473E6-FADB-4132-B869-00908FE5794E}"/>
+    <hyperlink ref="A130" r:id="rId111" xr:uid="{8BDF95B1-E2F5-421F-9023-ABFC8B1F48B1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="4">
@@ -5892,7 +5892,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" ht="13.8">
       <c r="A10" s="14" t="s">
         <v>36</v>
       </c>
@@ -5903,7 +5903,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" ht="13.8">
       <c r="A11" s="19" t="s">
         <v>71</v>
       </c>

--- a/Riyadh_Zone_Eng_Log.xlsx
+++ b/Riyadh_Zone_Eng_Log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\SOCOTEC_VISITS App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DB2763-D174-4549-A02B-95CE3703C68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702B9A91-E393-462A-BE17-F3BABA9857CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1477,8 +1477,8 @@
   <dimension ref="A1:G184"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.44140625" customWidth="1"/>
+    <col min="1" max="1" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="15.44140625" customWidth="1"/>
     <col min="5" max="5" width="22.109375" customWidth="1"/>
@@ -3971,11 +3971,11 @@
       </c>
     </row>
     <row r="109" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A109" s="4" t="s">
-        <v>20</v>
+      <c r="A109" s="21" t="s">
+        <v>148</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>150</v>
@@ -3994,11 +3994,11 @@
       </c>
     </row>
     <row r="110" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A110" s="4" t="s">
-        <v>20</v>
+      <c r="A110" s="21" t="s">
+        <v>148</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="C110" s="10" t="s">
         <v>150</v>
@@ -4017,11 +4017,11 @@
       </c>
     </row>
     <row r="111" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A111" s="4" t="s">
-        <v>20</v>
+      <c r="A111" s="21" t="s">
+        <v>148</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>150</v>
@@ -4040,11 +4040,11 @@
       </c>
     </row>
     <row r="112" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A112" s="4" t="s">
-        <v>20</v>
+      <c r="A112" s="21" t="s">
+        <v>148</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="C112" s="10" t="s">
         <v>150</v>
@@ -4063,11 +4063,11 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A113" s="4" t="s">
-        <v>20</v>
+      <c r="A113" s="21" t="s">
+        <v>148</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>150</v>
@@ -4086,11 +4086,11 @@
       </c>
     </row>
     <row r="114" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A114" s="4" t="s">
-        <v>20</v>
+      <c r="A114" s="21" t="s">
+        <v>148</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>150</v>
@@ -4109,11 +4109,11 @@
       </c>
     </row>
     <row r="115" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A115" s="4" t="s">
-        <v>20</v>
+      <c r="A115" s="21" t="s">
+        <v>148</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>150</v>
@@ -4132,11 +4132,11 @@
       </c>
     </row>
     <row r="116" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A116" s="4" t="s">
-        <v>20</v>
+      <c r="A116" s="21" t="s">
+        <v>148</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>150</v>
@@ -4155,11 +4155,11 @@
       </c>
     </row>
     <row r="117" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A117" s="4" t="s">
-        <v>20</v>
+      <c r="A117" s="21" t="s">
+        <v>148</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="C117" s="10" t="s">
         <v>150</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="118" spans="1:7" ht="22.5" customHeight="1">
       <c r="A118" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B118" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C118" s="10" t="s">
         <v>150</v>
@@ -4202,10 +4202,10 @@
     </row>
     <row r="119" spans="1:7" ht="22.5" customHeight="1">
       <c r="A119" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B119" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>150</v>
@@ -4225,10 +4225,10 @@
     </row>
     <row r="120" spans="1:7" ht="22.5" customHeight="1">
       <c r="A120" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B120" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>150</v>
@@ -4248,10 +4248,10 @@
     </row>
     <row r="121" spans="1:7" ht="22.5" customHeight="1">
       <c r="A121" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B121" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>150</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="122" spans="1:7" ht="22.5" customHeight="1">
       <c r="A122" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B122" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>150</v>
@@ -4294,10 +4294,10 @@
     </row>
     <row r="123" spans="1:7" ht="22.5" customHeight="1">
       <c r="A123" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B123" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>150</v>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="124" spans="1:7" ht="22.5" customHeight="1">
       <c r="A124" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B124" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>150</v>
@@ -4340,10 +4340,10 @@
     </row>
     <row r="125" spans="1:7" ht="22.5" customHeight="1">
       <c r="A125" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B125" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>150</v>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="126" spans="1:7" ht="22.5" customHeight="1">
       <c r="A126" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B126" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>150</v>
@@ -4386,10 +4386,10 @@
     </row>
     <row r="127" spans="1:7" ht="22.5" customHeight="1">
       <c r="A127" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>150</v>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="128" spans="1:7" ht="22.5" customHeight="1">
       <c r="A128" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B128" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>150</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="129" spans="1:7" ht="22.5" customHeight="1">
       <c r="A129" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B129" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>150</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="130" spans="1:7" ht="22.5" customHeight="1">
       <c r="A130" s="21" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B130" s="23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>150</v>
@@ -5737,35 +5737,15 @@
     <hyperlink ref="A184" r:id="rId87" xr:uid="{F3225E6D-3468-4318-8B91-260F9EF96990}"/>
     <hyperlink ref="A166" r:id="rId88" xr:uid="{28C032BE-745B-4719-BC4F-5BC8CF6CE6AD}"/>
     <hyperlink ref="A167:A180" r:id="rId89" display="ayman.ashraf@socotec.com" xr:uid="{74B3E606-0774-48D2-9E42-2C52AF79F7BD}"/>
-    <hyperlink ref="A109" r:id="rId90" xr:uid="{B85E91F0-F4EA-411E-88CC-88F74EEC2B12}"/>
-    <hyperlink ref="A110" r:id="rId91" xr:uid="{31B92A57-38BB-4EB0-9730-087D7EE8F96E}"/>
-    <hyperlink ref="A111" r:id="rId92" xr:uid="{AF65F850-7986-4660-98A9-CED467115EE6}"/>
-    <hyperlink ref="A112" r:id="rId93" xr:uid="{FAA039C4-A032-49DC-9FCF-95ECD6932EB3}"/>
-    <hyperlink ref="A113" r:id="rId94" xr:uid="{9E2C83CD-3637-4CE4-916D-D485033DB5E1}"/>
-    <hyperlink ref="A114" r:id="rId95" xr:uid="{41BEEFAF-AD8A-4B84-B398-82653F7106E0}"/>
-    <hyperlink ref="A115" r:id="rId96" xr:uid="{7469C548-438F-45DA-B067-D2855D4DD123}"/>
-    <hyperlink ref="A116" r:id="rId97" xr:uid="{222237D1-C95A-41A2-A813-10E3D5079802}"/>
-    <hyperlink ref="A117" r:id="rId98" xr:uid="{039B2F75-D7CC-4948-A090-EF878C0B6E96}"/>
-    <hyperlink ref="A118" r:id="rId99" xr:uid="{1D2F319C-7082-44EB-ABA8-0F6C7FC5B9DE}"/>
-    <hyperlink ref="A119" r:id="rId100" xr:uid="{22AE1928-7CBF-4A84-8D9F-AEF119A564CA}"/>
-    <hyperlink ref="A120" r:id="rId101" xr:uid="{B1500585-3756-49B3-B698-2222CCE9F14E}"/>
-    <hyperlink ref="A121" r:id="rId102" xr:uid="{968959D0-FA97-450C-ACD2-5CF200080073}"/>
-    <hyperlink ref="A122" r:id="rId103" xr:uid="{569040FD-28EE-485E-AF7B-C1F4A17863D5}"/>
-    <hyperlink ref="A123" r:id="rId104" xr:uid="{F1712F73-9AFA-4A1A-8459-949196FF4947}"/>
-    <hyperlink ref="A124" r:id="rId105" xr:uid="{F3B030FA-01EC-4BBA-8F9D-2F23126EACBA}"/>
-    <hyperlink ref="A125" r:id="rId106" xr:uid="{09036006-CF36-48E2-B1F1-5561E5001113}"/>
-    <hyperlink ref="A126" r:id="rId107" xr:uid="{151F7DF0-58AC-46D8-AF5F-4800D407AF9A}"/>
-    <hyperlink ref="A127" r:id="rId108" xr:uid="{3B52CF30-7D13-48A7-94F4-70F57714E363}"/>
-    <hyperlink ref="A128" r:id="rId109" xr:uid="{089C5B9B-4DAC-4B8F-8F15-F80D0FEC277F}"/>
-    <hyperlink ref="A129" r:id="rId110" xr:uid="{214473E6-FADB-4132-B869-00908FE5794E}"/>
-    <hyperlink ref="A130" r:id="rId111" xr:uid="{8BDF95B1-E2F5-421F-9023-ABFC8B1F48B1}"/>
+    <hyperlink ref="A109" r:id="rId90" xr:uid="{DD1309C6-0941-4B5D-BCB2-777E877BE9CD}"/>
+    <hyperlink ref="A110:A130" r:id="rId91" display="saeed.alqahtani@socotec.com" xr:uid="{DB657724-650C-41B1-AC9B-955B16741BFC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="4">
-    <tablePart r:id="rId112"/>
-    <tablePart r:id="rId113"/>
-    <tablePart r:id="rId114"/>
-    <tablePart r:id="rId115"/>
+    <tablePart r:id="rId92"/>
+    <tablePart r:id="rId93"/>
+    <tablePart r:id="rId94"/>
+    <tablePart r:id="rId95"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/Riyadh_Zone_Eng_Log.xlsx
+++ b/Riyadh_Zone_Eng_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\SOCOTEC_VISITS App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702B9A91-E393-462A-BE17-F3BABA9857CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2B6807-8075-4E8B-9998-AA221ACAEFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3038,38 +3038,38 @@
         <v>87</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G68" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="22.5" customHeight="1">
       <c r="A69" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="B69" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="D69" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D69" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G69" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3084,15 +3084,15 @@
         <v>108</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G70" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G70" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3107,15 +3107,15 @@
         <v>108</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F71" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G71" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3130,15 +3130,15 @@
         <v>108</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G72" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G72" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3153,15 +3153,15 @@
         <v>108</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F73" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G73" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G73" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3176,15 +3176,15 @@
         <v>108</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G74" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G74" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3199,15 +3199,15 @@
         <v>108</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E75" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F75" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G75" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G75" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3222,15 +3222,15 @@
         <v>108</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G76" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G76" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3245,15 +3245,15 @@
         <v>108</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F77" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G77" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3268,15 +3268,15 @@
         <v>108</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G78" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G78" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3291,15 +3291,15 @@
         <v>108</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E79" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F79" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G79" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G79" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3314,15 +3314,15 @@
         <v>108</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G80" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G80" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3337,15 +3337,15 @@
         <v>108</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="E81" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F81" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G81" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3360,15 +3360,15 @@
         <v>108</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G82" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G82" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3383,15 +3383,15 @@
         <v>108</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="E83" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F83" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G83" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G83" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3406,15 +3406,15 @@
         <v>108</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G84" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G84" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3429,15 +3429,15 @@
         <v>108</v>
       </c>
       <c r="D85" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="E85" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F85" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G85" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G85" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3452,15 +3452,15 @@
         <v>108</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G86" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G86" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3475,15 +3475,15 @@
         <v>108</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="E87" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F87" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G87" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G87" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3498,15 +3498,15 @@
         <v>108</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G88" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G88" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3521,15 +3521,15 @@
         <v>108</v>
       </c>
       <c r="D89" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E89" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F89" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G89" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G89" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3544,15 +3544,15 @@
         <v>108</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G90" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E90" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F90" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G90" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3567,15 +3567,15 @@
         <v>108</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="E91" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F91" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G91" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G91" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3590,15 +3590,15 @@
         <v>108</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G92" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E92" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F92" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G92" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3613,15 +3613,15 @@
         <v>108</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="E93" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F93" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G93" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G93" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3636,15 +3636,15 @@
         <v>108</v>
       </c>
       <c r="D94" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G94" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E94" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G94" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3659,15 +3659,15 @@
         <v>108</v>
       </c>
       <c r="D95" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="E95" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F95" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G95" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G95" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3682,15 +3682,15 @@
         <v>108</v>
       </c>
       <c r="D96" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G96" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E96" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G96" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3705,15 +3705,15 @@
         <v>108</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="E97" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F97" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G97" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G97" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3728,15 +3728,15 @@
         <v>108</v>
       </c>
       <c r="D98" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G98" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E98" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F98" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G98" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3751,15 +3751,15 @@
         <v>108</v>
       </c>
       <c r="D99" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="E99" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F99" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G99" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G99" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3774,15 +3774,15 @@
         <v>108</v>
       </c>
       <c r="D100" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G100" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E100" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F100" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G100" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3797,15 +3797,15 @@
         <v>108</v>
       </c>
       <c r="D101" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="E101" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F101" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G101" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G101" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3820,15 +3820,15 @@
         <v>108</v>
       </c>
       <c r="D102" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="E102" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F102" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G102" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E102" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F102" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G102" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3843,15 +3843,15 @@
         <v>108</v>
       </c>
       <c r="D103" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="E103" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F103" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G103" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G103" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3866,15 +3866,15 @@
         <v>108</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G104" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E104" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F104" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G104" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3889,15 +3889,15 @@
         <v>108</v>
       </c>
       <c r="D105" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E105" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F105" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G105" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G105" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3912,15 +3912,15 @@
         <v>108</v>
       </c>
       <c r="D106" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G106" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E106" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F106" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G106" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3935,15 +3935,15 @@
         <v>108</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="E107" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F107" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G107" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G107" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
         <v>108</v>
       </c>
       <c r="D108" s="23" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="E108" s="8" t="s">
         <v>24</v>
@@ -5682,63 +5682,63 @@
     <hyperlink ref="A65" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
     <hyperlink ref="A66" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
     <hyperlink ref="A67" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="A68" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="A69" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="A70" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="A71" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="A72" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="A73" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="A74" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="A75" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="A76" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="A77" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="A78" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="A79" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="A80" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="A81" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="A82" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="A83" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="A84" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="A85" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="A86" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="A87" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="A88" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="A89" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="A90" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="A91" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="A92" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="A93" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="A94" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="A95" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="A96" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="A97" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="A98" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="A99" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="A100" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="A101" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="A102" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="A103" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="A104" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="A105" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="A106" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="A107" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="A108" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="A156" r:id="rId76" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="A157" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="A158" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="A159" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="A160" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="A161" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="A162" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="A163" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="A164" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="A165" r:id="rId85" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="A181" r:id="rId86" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="A184" r:id="rId87" xr:uid="{F3225E6D-3468-4318-8B91-260F9EF96990}"/>
-    <hyperlink ref="A166" r:id="rId88" xr:uid="{28C032BE-745B-4719-BC4F-5BC8CF6CE6AD}"/>
-    <hyperlink ref="A167:A180" r:id="rId89" display="ayman.ashraf@socotec.com" xr:uid="{74B3E606-0774-48D2-9E42-2C52AF79F7BD}"/>
-    <hyperlink ref="A109" r:id="rId90" xr:uid="{DD1309C6-0941-4B5D-BCB2-777E877BE9CD}"/>
-    <hyperlink ref="A110:A130" r:id="rId91" display="saeed.alqahtani@socotec.com" xr:uid="{DB657724-650C-41B1-AC9B-955B16741BFC}"/>
+    <hyperlink ref="A68" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="A69" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="A70" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="A71" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="A72" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="A73" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="A74" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="A75" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="A76" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="A77" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="A78" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="A79" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="A80" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="A81" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="A82" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="A83" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="A84" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="A85" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="A86" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="A87" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="A88" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="A89" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="A90" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="A91" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="A92" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="A93" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="A94" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="A95" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="A96" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="A97" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="A98" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="A99" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="A100" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="A101" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="A102" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="A103" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="A104" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="A105" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="A106" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="A107" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="A156" r:id="rId75" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="A157" r:id="rId76" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="A158" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="A159" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="A160" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="A161" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="A162" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="A163" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="A164" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="A165" r:id="rId84" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="A181" r:id="rId85" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="A184" r:id="rId86" xr:uid="{F3225E6D-3468-4318-8B91-260F9EF96990}"/>
+    <hyperlink ref="A166" r:id="rId87" xr:uid="{28C032BE-745B-4719-BC4F-5BC8CF6CE6AD}"/>
+    <hyperlink ref="A167:A180" r:id="rId88" display="ayman.ashraf@socotec.com" xr:uid="{74B3E606-0774-48D2-9E42-2C52AF79F7BD}"/>
+    <hyperlink ref="A109" r:id="rId89" xr:uid="{DD1309C6-0941-4B5D-BCB2-777E877BE9CD}"/>
+    <hyperlink ref="A110:A130" r:id="rId90" display="saeed.alqahtani@socotec.com" xr:uid="{DB657724-650C-41B1-AC9B-955B16741BFC}"/>
+    <hyperlink ref="A108" r:id="rId91" xr:uid="{B457B613-A45D-4E3A-81A3-B522C076D6C8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="4">
